--- a/output/pdf_financials_xlsx/TCO.xlsx
+++ b/output/pdf_financials_xlsx/TCO.xlsx
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>5.796263</v>
+        <v>-5.796263</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.142217</v>
+        <v>-2.142217</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-6.456617</v>
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>5.796263</v>
+        <v>-5.796263</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2.142217</v>
+        <v>-2.142217</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-6.456617</v>
@@ -1400,10 +1400,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>5.796263</v>
+        <v>-5.796263</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2.142217</v>
+        <v>-2.142217</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-6.456617</v>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>82.803757</v>
+        <v>-82.803757</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>107.11085</v>
+        <v>-107.11085</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>15.015388</v>
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>5.796263</v>
+        <v>-5.796263</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2.142217</v>
+        <v>-2.142217</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-6.456617</v>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>5.796263</v>
+        <v>-5.796263</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2.142217</v>
+        <v>-2.142217</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-6.456617</v>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -4459,40 +4459,40 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.6334959999999999</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.954278</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.957067</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.773271</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.845952</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.845952</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>4.405872</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.405872</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>4.405872</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>4.405872</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>4.405872</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>5.510658</v>
       </c>
     </row>
     <row r="93">
@@ -7616,7 +7616,11 @@
           <t>Share-based payment reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -8136,7 +8140,11 @@
           <t>Share-based payment reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -8886,7 +8894,11 @@
           <t>Share-based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -9646,7 +9658,11 @@
           <t>Share-based payment reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -10480,7 +10496,11 @@
           <t>Share-based payment reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -11092,7 +11112,11 @@
           <t>Share-based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -11774,7 +11798,11 @@
           <t>Share-based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -12148,7 +12176,11 @@
           <t>Share-based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -12658,7 +12690,11 @@
           <t>Share-based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E84" s="5" t="n">
         <v>0.6334959999999999</v>
       </c>
@@ -25835,7 +25871,7 @@
         </is>
       </c>
       <c r="F266" s="5" t="n">
-        <v>2.142217</v>
+        <v>-2.142217</v>
       </c>
       <c r="G266" s="5" t="n">
         <v>-6.456617</v>
@@ -27700,10 +27736,10 @@
         </is>
       </c>
       <c r="E291" s="5" t="n">
-        <v>5.796263</v>
+        <v>-5.796263</v>
       </c>
       <c r="F291" s="5" t="n">
-        <v>2.142217</v>
+        <v>-2.142217</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/TCO.xlsx
+++ b/output/pdf_financials_xlsx/TCO.xlsx
@@ -897,22 +897,22 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.050424</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.207425</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.165889</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.055775</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.03766</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.028152</v>
       </c>
     </row>
     <row r="13">
@@ -1604,22 +1604,22 @@
         <v>-1.105574</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>7.605107</v>
+        <v>7.554683</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.425107</v>
+        <v>-1.632532</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-3.679069</v>
+        <v>-3.844958</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.803752</v>
+        <v>-0.859527</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.285292</v>
+        <v>-0.322952</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.971662</v>
+        <v>-0.999814</v>
       </c>
     </row>
     <row r="28">
@@ -1690,22 +1690,22 @@
         <v>-1.105574</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>7.605107</v>
+        <v>7.554683</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.425107</v>
+        <v>-1.632532</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-3.679069</v>
+        <v>-3.844958</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.803752</v>
+        <v>-0.859527</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.285292</v>
+        <v>-0.322952</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.971662</v>
+        <v>-0.999814</v>
       </c>
     </row>
     <row r="30">
@@ -1899,25 +1899,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.000428</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.190021</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.104909</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.08024299999999999</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.127211</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.033248</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.774448</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0.568068</v>
@@ -1929,10 +1929,10 @@
         <v>1.03162</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.148542</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.788271</v>
       </c>
     </row>
     <row r="35">
@@ -1985,25 +1985,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.000428</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.190021</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.104909</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.08024299999999999</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.127211</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.033248</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.774448</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.568068</v>
@@ -2015,10 +2015,10 @@
         <v>1.69292</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.58778</v>
+        <v>1.736322</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.788271</v>
       </c>
     </row>
     <row r="37">
@@ -2501,25 +2501,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.024168</v>
+        <v>0.02374</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.22503</v>
+        <v>0.035009</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.209412</v>
+        <v>0.104503</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.163711</v>
+        <v>0.083468</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.146954</v>
+        <v>0.019743</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.051041</v>
+        <v>0.017793</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>6.851814</v>
+        <v>6.077366</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>4.41887</v>
@@ -2531,10 +2531,10 @@
         <v>1.502839</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.970627</v>
+        <v>0.822085</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.826389</v>
+        <v>1.038118</v>
       </c>
     </row>
     <row r="49">
@@ -5879,10 +5879,10 @@
         <v>0</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.005347</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.002114</v>
       </c>
       <c r="H124" s="3" t="n">
         <v>0</v>
@@ -5924,10 +5924,10 @@
         <v>0</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.005347</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.002114</v>
       </c>
       <c r="H125" s="3" t="n">
         <v>0</v>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -17630,7 +17630,11 @@
           <t>Lease payment</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -20706,7 +20710,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -22654,7 +22658,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">

--- a/output/pdf_financials_xlsx/TCO.xlsx
+++ b/output/pdf_financials_xlsx/TCO.xlsx
@@ -3213,40 +3213,40 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.421752</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.347511</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>1.521405</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.847816</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>1.329581</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>1.599133</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>1.559446</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.620526</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.798682</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.60353</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.510192</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.511379</v>
       </c>
     </row>
     <row r="65">
@@ -3342,40 +3342,40 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.03894</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.041118</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.018941</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.1512</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.166</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.204758</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.161735</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.288333</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.247586</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.22398</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.219598</v>
       </c>
     </row>
     <row r="68">
@@ -5228,16 +5228,16 @@
         <v>0</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.09585100000000001</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.342146</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.047368</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.158669</v>
       </c>
       <c r="I110" s="3" t="n">
         <v>0</v>
@@ -5267,34 +5267,34 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.06982099999999999</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.860737</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.323478</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003784</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005398</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.038021</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.021718</v>
       </c>
       <c r="K111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.038839</v>
       </c>
       <c r="M111" s="1" t="inlineStr">
         <is>
@@ -6404,34 +6404,34 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.06982099999999999</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.860737</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.323478</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003784</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005398</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.038021</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.021718</v>
       </c>
       <c r="K134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.038839</v>
       </c>
       <c r="M134" s="1" t="inlineStr">
         <is>
@@ -6461,10 +6461,10 @@
         </is>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-1.393538</v>
+        <v>-1.717016</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-0.471711</v>
+        <v>-0.475495</v>
       </c>
       <c r="G135" s="1" t="inlineStr">
         <is>
@@ -14010,7 +14010,11 @@
           <t>Proceeds from short term investment</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -14084,7 +14088,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -15754,7 +15762,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -17340,7 +17352,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -18646,7 +18662,11 @@
           <t>Private placements</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
